--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.73847</v>
+        <v>17.68721</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15671</v>
+        <v>17.43449</v>
       </c>
       <c r="E2" t="n">
-        <v>17.21773</v>
+        <v>17.53597</v>
       </c>
       <c r="F2" t="n">
-        <v>44.88414</v>
+        <v>44.04772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05227</v>
+        <v>0.0544</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8655</v>
+        <v>1.9242</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.55034</v>
+        <v>17.50747</v>
       </c>
       <c r="D3" t="n">
-        <v>17.39108</v>
+        <v>16.82465</v>
       </c>
       <c r="E3" t="n">
-        <v>17.46808</v>
+        <v>17.41804</v>
       </c>
       <c r="F3" t="n">
-        <v>44.40138</v>
+        <v>43.92534</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05284</v>
+        <v>0.05342</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94943</v>
+        <v>1.91373</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.68763</v>
+        <v>17.5891</v>
       </c>
       <c r="D4" t="n">
-        <v>17.3576</v>
+        <v>17.29065</v>
       </c>
       <c r="E4" t="n">
-        <v>17.13017</v>
+        <v>17.40921</v>
       </c>
       <c r="F4" t="n">
-        <v>44.22824</v>
+        <v>44.98972</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05277</v>
+        <v>0.05329</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89035</v>
+        <v>1.90417</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.49531</v>
+        <v>17.44776</v>
       </c>
       <c r="D6" t="n">
-        <v>16.99223</v>
+        <v>16.48164</v>
       </c>
       <c r="E6" t="n">
-        <v>17.19414</v>
+        <v>16.97849</v>
       </c>
       <c r="F6" t="n">
-        <v>22.61098</v>
+        <v>22.83362</v>
       </c>
       <c r="G6" t="n">
-        <v>36.26529</v>
+        <v>35.57182</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.29072</v>
+        <v>17.59536</v>
       </c>
       <c r="D7" t="n">
-        <v>16.60011</v>
+        <v>16.2813</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22507</v>
+        <v>17.09808</v>
       </c>
       <c r="F7" t="n">
-        <v>22.81041</v>
+        <v>23.18581</v>
       </c>
       <c r="G7" t="n">
-        <v>36.17717</v>
+        <v>35.36024</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.66709</v>
+        <v>17.40451</v>
       </c>
       <c r="D8" t="n">
-        <v>16.42511</v>
+        <v>16.33566</v>
       </c>
       <c r="E8" t="n">
-        <v>16.92902</v>
+        <v>17.25894</v>
       </c>
       <c r="F8" t="n">
-        <v>22.62506</v>
+        <v>23.34896</v>
       </c>
       <c r="G8" t="n">
-        <v>36.1755</v>
+        <v>35.83697</v>
       </c>
     </row>
   </sheetData>
